--- a/Respostas.xlsx
+++ b/Respostas.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29103"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01879CDA-4CC9-44A6-B71D-E81FFECA330C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7547E00A-06C3-4A95-A9F4-584810623649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="132" windowWidth="16212" windowHeight="8448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="132" windowWidth="16212" windowHeight="8448" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Classe" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Componentes" sheetId="8" r:id="rId8"/>
     <sheet name="Máquina de estados" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -469,28 +469,6 @@
     </comment>
   </commentList>
 </comments>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4733,7 +4711,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
@@ -8236,36 +8214,7 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="15"/>
-    <row r="44" spans="1:8" ht="15">
-      <c r="B44" cm="1">
-        <f t="array" aca="1" ref="B44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(B$3:B$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="C44" cm="1">
-        <f t="array" aca="1" ref="C44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(C$3:C$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="D44" cm="1">
-        <f t="array" aca="1" ref="D44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(D$3:D$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="E44" cm="1">
-        <f t="array" aca="1" ref="E44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(E$3:E$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="F44" cm="1">
-        <f t="array" aca="1" ref="F44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(F$3:F$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="G44" cm="1">
-        <f t="array" aca="1" ref="G44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(G$3:G$44="✅"))</f>
-        <v>0</v>
-      </c>
-      <c r="H44" cm="1">
-        <f t="array" aca="1" ref="H44" ca="1">SUMPRODUCT(--ISNUMBER(SEARCH(".N.", $A$3:$A$44)), --(H$3:H$44="✅"))</f>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="44" spans="1:8" ht="15"/>
     <row r="45" spans="1:8" ht="15"/>
     <row r="46" spans="1:8" ht="15"/>
     <row r="47" spans="1:8" ht="15"/>
